--- a/output_data/charts/0500000US39097.xlsx
+++ b/output_data/charts/0500000US39097.xlsx
@@ -167,10 +167,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -212,16 +212,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$15</c:f>
+              <c:f>Sheet1!$B$2:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.5709812589215821</c:v>
                 </c:pt>
@@ -253,16 +256,19 @@
                   <c:v>1.352316343836472</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.448151611211202</c:v>
+                  <c:v>1.447854439326919</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.494552984604304</c:v>
+                  <c:v>1.493914099939254</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.512126844266997</c:v>
+                  <c:v>1.508724462889505</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.573920451997668</c:v>
+                  <c:v>1.580549834333303</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.704333311370275</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -292,10 +298,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -337,16 +343,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$15</c:f>
+              <c:f>Sheet1!$C$2:$C$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>6.522539945664686</c:v>
                 </c:pt>
@@ -378,16 +387,19 @@
                   <c:v>6.299651878960992</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6.485894775251431</c:v>
+                  <c:v>6.489123991062064</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>6.813270910236787</c:v>
+                  <c:v>6.835106981348573</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5.949840526835088</c:v>
+                  <c:v>5.966111021942998</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>6.33603874265728</c:v>
+                  <c:v>6.344586728754366</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6.338538578111616</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -417,10 +429,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -462,16 +474,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$15</c:f>
+              <c:f>Sheet1!$D$2:$D$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.436662522447852</c:v>
                 </c:pt>
@@ -503,16 +518,19 @@
                   <c:v>2.385521735249487</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.798239412529362</c:v>
+                  <c:v>2.797665192211227</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.91482848654002</c:v>
+                  <c:v>2.913582469008032</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.122920538766894</c:v>
+                  <c:v>3.127507853163048</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.318236850365455</c:v>
+                  <c:v>3.353631234888511</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.494322549471788</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -542,10 +560,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -587,16 +605,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$15</c:f>
+              <c:f>Sheet1!$E$2:$E$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.2302343785974122</c:v>
                 </c:pt>
@@ -628,16 +649,19 @@
                   <c:v>0.3146478621797733</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.3147164131451117</c:v>
+                  <c:v>0.3146518309088421</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.3241199243720176</c:v>
+                  <c:v>0.3239813710711634</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.3533649985085244</c:v>
+                  <c:v>0.3531057253571183</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.3542442042957715</c:v>
+                  <c:v>0.3559595235963106</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.3492126243658167</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -667,10 +691,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -712,16 +736,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$15</c:f>
+              <c:f>Sheet1!$F$2:$F$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.32384767693512</c:v>
                 </c:pt>
@@ -753,16 +780,19 @@
                   <c:v>1.608944032848344</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.616912586375972</c:v>
+                  <c:v>1.621140954899904</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.631853785900784</c:v>
+                  <c:v>1.635655949782888</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.764530414630229</c:v>
+                  <c:v>1.788457569990599</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.847450786960226</c:v>
+                  <c:v>1.864869705381929</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.961301091563989</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -792,10 +822,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -837,16 +867,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$2:$G$15</c:f>
+              <c:f>Sheet1!$G$2:$G$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>89.91573421743335</c:v>
                 </c:pt>
@@ -878,16 +911,19 @@
                   <c:v>88.03891814692493</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>87.33608520148692</c:v>
+                  <c:v>87.32956359159104</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>86.82137390834609</c:v>
+                  <c:v>86.79775912885009</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>87.29721667699226</c:v>
+                  <c:v>87.25609336665673</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>86.5701089637236</c:v>
+                  <c:v>86.50040297304558</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>86.15229184511651</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1006,13 +1042,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1428750</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1320,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" style="1" customWidth="1"/>
@@ -1590,22 +1626,22 @@
         <v>2020</v>
       </c>
       <c r="B12" s="2">
-        <v>1.448151611211202</v>
+        <v>1.447854439326919</v>
       </c>
       <c r="C12" s="2">
-        <v>6.485894775251431</v>
+        <v>6.489123991062064</v>
       </c>
       <c r="D12" s="2">
-        <v>2.798239412529362</v>
+        <v>2.797665192211227</v>
       </c>
       <c r="E12" s="2">
-        <v>0.3147164131451117</v>
+        <v>0.3146518309088421</v>
       </c>
       <c r="F12" s="2">
-        <v>1.616912586375972</v>
+        <v>1.621140954899904</v>
       </c>
       <c r="G12" s="2">
-        <v>87.33608520148692</v>
+        <v>87.32956359159104</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1613,22 +1649,22 @@
         <v>2021</v>
       </c>
       <c r="B13" s="2">
-        <v>1.494552984604304</v>
+        <v>1.493914099939254</v>
       </c>
       <c r="C13" s="2">
-        <v>6.813270910236787</v>
+        <v>6.835106981348573</v>
       </c>
       <c r="D13" s="2">
-        <v>2.91482848654002</v>
+        <v>2.913582469008032</v>
       </c>
       <c r="E13" s="2">
-        <v>0.3241199243720176</v>
+        <v>0.3239813710711634</v>
       </c>
       <c r="F13" s="2">
-        <v>1.631853785900784</v>
+        <v>1.635655949782888</v>
       </c>
       <c r="G13" s="2">
-        <v>86.82137390834609</v>
+        <v>86.79775912885009</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1636,22 +1672,22 @@
         <v>2022</v>
       </c>
       <c r="B14" s="2">
-        <v>1.512126844266997</v>
+        <v>1.508724462889505</v>
       </c>
       <c r="C14" s="2">
-        <v>5.949840526835088</v>
+        <v>5.966111021942998</v>
       </c>
       <c r="D14" s="2">
-        <v>3.122920538766894</v>
+        <v>3.127507853163048</v>
       </c>
       <c r="E14" s="2">
-        <v>0.3533649985085244</v>
+        <v>0.3531057253571183</v>
       </c>
       <c r="F14" s="2">
-        <v>1.764530414630229</v>
+        <v>1.788457569990599</v>
       </c>
       <c r="G14" s="2">
-        <v>87.29721667699226</v>
+        <v>87.25609336665673</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1659,22 +1695,45 @@
         <v>2023</v>
       </c>
       <c r="B15" s="2">
-        <v>1.573920451997668</v>
+        <v>1.580549834333303</v>
       </c>
       <c r="C15" s="2">
-        <v>6.33603874265728</v>
+        <v>6.344586728754366</v>
       </c>
       <c r="D15" s="2">
-        <v>3.318236850365455</v>
+        <v>3.353631234888511</v>
       </c>
       <c r="E15" s="2">
-        <v>0.3542442042957715</v>
+        <v>0.3559595235963106</v>
       </c>
       <c r="F15" s="2">
-        <v>1.847450786960226</v>
+        <v>1.864869705381929</v>
       </c>
       <c r="G15" s="2">
-        <v>86.5701089637236</v>
+        <v>86.50040297304558</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1.704333311370275</v>
+      </c>
+      <c r="C16" s="2">
+        <v>6.338538578111616</v>
+      </c>
+      <c r="D16" s="2">
+        <v>3.494322549471788</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.3492126243658167</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1.961301091563989</v>
+      </c>
+      <c r="G16" s="2">
+        <v>86.15229184511651</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/0500000US39097.xlsx
+++ b/output_data/charts/0500000US39097.xlsx
@@ -229,31 +229,31 @@
                   <c:v>0.5709812589215821</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.6702226345083488</c:v>
+                  <c:v>0.663357610057058</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.7512326728067727</c:v>
+                  <c:v>0.744341838989556</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.8390541571319604</c:v>
+                  <c:v>0.8322544849269465</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.002546148949713</c:v>
+                  <c:v>0.995907230559345</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.146118824888446</c:v>
+                  <c:v>1.137316205623145</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.276497695852534</c:v>
+                  <c:v>1.293312123936648</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.318147786827597</c:v>
+                  <c:v>1.353284439499557</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.369585294978938</c:v>
+                  <c:v>1.412512108855798</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.352316343836472</c:v>
+                  <c:v>1.399476872862221</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1.447854439326919</c:v>
@@ -360,31 +360,31 @@
                   <c:v>6.522539945664686</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.333487940630798</c:v>
+                  <c:v>6.329730481978012</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.363382640245605</c:v>
+                  <c:v>6.364122723360703</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.23165291357511</c:v>
+                  <c:v>6.228037728869984</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.465399654451214</c:v>
+                  <c:v>6.462028194633924</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.525629119572357</c:v>
+                  <c:v>6.520310836221935</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.997695852534562</c:v>
+                  <c:v>6.005486778707611</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.42511967692901</c:v>
+                  <c:v>6.432642310574238</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.221701619624715</c:v>
+                  <c:v>6.233526324089302</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6.299651878960992</c:v>
+                  <c:v>6.33788647693993</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>6.489123991062064</c:v>
@@ -491,31 +491,31 @@
                   <c:v>1.436662522447852</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.479591836734694</c:v>
+                  <c:v>1.479797745511899</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.49781375011629</c:v>
+                  <c:v>1.495661882719639</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.754385964912281</c:v>
+                  <c:v>1.750046236360274</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.82549786305356</c:v>
+                  <c:v>1.819008640291041</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.843756370472717</c:v>
+                  <c:v>1.839642946147398</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.981566820276498</c:v>
+                  <c:v>1.952647716531803</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.082718878326565</c:v>
+                  <c:v>2.039009105152018</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.16700831212128</c:v>
+                  <c:v>2.10637770618847</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.385521735249487</c:v>
+                  <c:v>2.25347074735642</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2.797665192211227</c:v>
@@ -622,31 +622,31 @@
                   <c:v>0.2302343785974122</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.2249536178107607</c:v>
+                  <c:v>0.2296237880966739</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2302539771141502</c:v>
+                  <c:v>0.237258961177921</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2265215079860389</c:v>
+                  <c:v>0.2358054373959682</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2546148949713558</c:v>
+                  <c:v>0.2683037744429286</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2627466080771931</c:v>
+                  <c:v>0.2786651260789778</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2741935483870968</c:v>
+                  <c:v>0.2881711506097702</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.2972071601969281</c:v>
+                  <c:v>0.3110737721668445</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3041019980627576</c:v>
+                  <c:v>0.3221518844758837</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.3146478621797733</c:v>
+                  <c:v>0.3331023227739152</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.3146518309088421</c:v>
@@ -753,31 +753,31 @@
                   <c:v>1.32384767693512</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.403061224489796</c:v>
+                  <c:v>1.400937050610011</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.395478649176668</c:v>
+                  <c:v>1.38866274336489</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.405357927097058</c:v>
+                  <c:v>1.403273534307379</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.473129035191416</c:v>
+                  <c:v>1.464301955434288</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.494937597680582</c:v>
+                  <c:v>1.481682865493101</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.506912442396313</c:v>
+                  <c:v>1.493879244761048</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.604011162284184</c:v>
+                  <c:v>1.580345587066597</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.556551708602708</c:v>
+                  <c:v>1.538669490189011</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.608944032848344</c:v>
+                  <c:v>1.589501687867475</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1.621140954899904</c:v>
@@ -884,31 +884,31 @@
                   <c:v>89.91573421743335</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>89.88868274582561</c:v>
+                  <c:v>89.89655332374635</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>89.76183831054053</c:v>
+                  <c:v>89.76995185038729</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>89.54302752929755</c:v>
+                  <c:v>89.55058257813945</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>88.97881240338275</c:v>
+                  <c:v>88.99045020463848</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>88.72681147930871</c:v>
+                  <c:v>88.74238202043544</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>88.963133640553</c:v>
+                  <c:v>88.96650298545312</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>88.27279533543572</c:v>
+                  <c:v>88.28364478554074</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>88.3810510666096</c:v>
+                  <c:v>88.38676248620153</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>88.03891814692493</c:v>
+                  <c:v>88.08656189220004</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>87.32956359159104</c:v>
@@ -1419,22 +1419,22 @@
         <v>2011</v>
       </c>
       <c r="B3" s="2">
-        <v>0.6702226345083488</v>
+        <v>0.663357610057058</v>
       </c>
       <c r="C3" s="2">
-        <v>6.333487940630798</v>
+        <v>6.329730481978012</v>
       </c>
       <c r="D3" s="2">
-        <v>1.479591836734694</v>
+        <v>1.479797745511899</v>
       </c>
       <c r="E3" s="2">
-        <v>0.2249536178107607</v>
+        <v>0.2296237880966739</v>
       </c>
       <c r="F3" s="2">
-        <v>1.403061224489796</v>
+        <v>1.400937050610011</v>
       </c>
       <c r="G3" s="2">
-        <v>89.88868274582561</v>
+        <v>89.89655332374635</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1442,22 +1442,22 @@
         <v>2012</v>
       </c>
       <c r="B4" s="2">
-        <v>0.7512326728067727</v>
+        <v>0.744341838989556</v>
       </c>
       <c r="C4" s="2">
-        <v>6.363382640245605</v>
+        <v>6.364122723360703</v>
       </c>
       <c r="D4" s="2">
-        <v>1.49781375011629</v>
+        <v>1.495661882719639</v>
       </c>
       <c r="E4" s="2">
-        <v>0.2302539771141502</v>
+        <v>0.237258961177921</v>
       </c>
       <c r="F4" s="2">
-        <v>1.395478649176668</v>
+        <v>1.38866274336489</v>
       </c>
       <c r="G4" s="2">
-        <v>89.76183831054053</v>
+        <v>89.76995185038729</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1465,22 +1465,22 @@
         <v>2013</v>
       </c>
       <c r="B5" s="2">
-        <v>0.8390541571319604</v>
+        <v>0.8322544849269465</v>
       </c>
       <c r="C5" s="2">
-        <v>6.23165291357511</v>
+        <v>6.228037728869984</v>
       </c>
       <c r="D5" s="2">
-        <v>1.754385964912281</v>
+        <v>1.750046236360274</v>
       </c>
       <c r="E5" s="2">
-        <v>0.2265215079860389</v>
+        <v>0.2358054373959682</v>
       </c>
       <c r="F5" s="2">
-        <v>1.405357927097058</v>
+        <v>1.403273534307379</v>
       </c>
       <c r="G5" s="2">
-        <v>89.54302752929755</v>
+        <v>89.55058257813945</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1488,22 +1488,22 @@
         <v>2014</v>
       </c>
       <c r="B6" s="2">
-        <v>1.002546148949713</v>
+        <v>0.995907230559345</v>
       </c>
       <c r="C6" s="2">
-        <v>6.465399654451214</v>
+        <v>6.462028194633924</v>
       </c>
       <c r="D6" s="2">
-        <v>1.82549786305356</v>
+        <v>1.819008640291041</v>
       </c>
       <c r="E6" s="2">
-        <v>0.2546148949713558</v>
+        <v>0.2683037744429286</v>
       </c>
       <c r="F6" s="2">
-        <v>1.473129035191416</v>
+        <v>1.464301955434288</v>
       </c>
       <c r="G6" s="2">
-        <v>88.97881240338275</v>
+        <v>88.99045020463848</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1511,22 +1511,22 @@
         <v>2015</v>
       </c>
       <c r="B7" s="2">
-        <v>1.146118824888446</v>
+        <v>1.137316205623145</v>
       </c>
       <c r="C7" s="2">
-        <v>6.525629119572357</v>
+        <v>6.520310836221935</v>
       </c>
       <c r="D7" s="2">
-        <v>1.843756370472717</v>
+        <v>1.839642946147398</v>
       </c>
       <c r="E7" s="2">
-        <v>0.2627466080771931</v>
+        <v>0.2786651260789778</v>
       </c>
       <c r="F7" s="2">
-        <v>1.494937597680582</v>
+        <v>1.481682865493101</v>
       </c>
       <c r="G7" s="2">
-        <v>88.72681147930871</v>
+        <v>88.74238202043544</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1534,22 +1534,22 @@
         <v>2016</v>
       </c>
       <c r="B8" s="2">
-        <v>1.276497695852534</v>
+        <v>1.293312123936648</v>
       </c>
       <c r="C8" s="2">
-        <v>5.997695852534562</v>
+        <v>6.005486778707611</v>
       </c>
       <c r="D8" s="2">
-        <v>1.981566820276498</v>
+        <v>1.952647716531803</v>
       </c>
       <c r="E8" s="2">
-        <v>0.2741935483870968</v>
+        <v>0.2881711506097702</v>
       </c>
       <c r="F8" s="2">
-        <v>1.506912442396313</v>
+        <v>1.493879244761048</v>
       </c>
       <c r="G8" s="2">
-        <v>88.963133640553</v>
+        <v>88.96650298545312</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1557,22 +1557,22 @@
         <v>2017</v>
       </c>
       <c r="B9" s="2">
-        <v>1.318147786827597</v>
+        <v>1.353284439499557</v>
       </c>
       <c r="C9" s="2">
-        <v>6.42511967692901</v>
+        <v>6.432642310574238</v>
       </c>
       <c r="D9" s="2">
-        <v>2.082718878326565</v>
+        <v>2.039009105152018</v>
       </c>
       <c r="E9" s="2">
-        <v>0.2972071601969281</v>
+        <v>0.3110737721668445</v>
       </c>
       <c r="F9" s="2">
-        <v>1.604011162284184</v>
+        <v>1.580345587066597</v>
       </c>
       <c r="G9" s="2">
-        <v>88.27279533543572</v>
+        <v>88.28364478554074</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1580,22 +1580,22 @@
         <v>2018</v>
       </c>
       <c r="B10" s="2">
-        <v>1.369585294978938</v>
+        <v>1.412512108855798</v>
       </c>
       <c r="C10" s="2">
-        <v>6.221701619624715</v>
+        <v>6.233526324089302</v>
       </c>
       <c r="D10" s="2">
-        <v>2.16700831212128</v>
+        <v>2.10637770618847</v>
       </c>
       <c r="E10" s="2">
-        <v>0.3041019980627576</v>
+        <v>0.3221518844758837</v>
       </c>
       <c r="F10" s="2">
-        <v>1.556551708602708</v>
+        <v>1.538669490189011</v>
       </c>
       <c r="G10" s="2">
-        <v>88.3810510666096</v>
+        <v>88.38676248620153</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1603,22 +1603,22 @@
         <v>2019</v>
       </c>
       <c r="B11" s="2">
-        <v>1.352316343836472</v>
+        <v>1.399476872862221</v>
       </c>
       <c r="C11" s="2">
-        <v>6.299651878960992</v>
+        <v>6.33788647693993</v>
       </c>
       <c r="D11" s="2">
-        <v>2.385521735249487</v>
+        <v>2.25347074735642</v>
       </c>
       <c r="E11" s="2">
-        <v>0.3146478621797733</v>
+        <v>0.3331023227739152</v>
       </c>
       <c r="F11" s="2">
-        <v>1.608944032848344</v>
+        <v>1.589501687867475</v>
       </c>
       <c r="G11" s="2">
-        <v>88.03891814692493</v>
+        <v>88.08656189220004</v>
       </c>
     </row>
     <row r="12" spans="1:7">
